--- a/data/trans_dic/P16A02-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A02-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,25; 15,38</t>
+          <t>9,79; 15,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,94; 17,13</t>
+          <t>9,74; 16,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,12; 23,84</t>
+          <t>15,96; 23,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,35; 22,65</t>
+          <t>15,22; 22,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,99; 25,07</t>
+          <t>15,87; 25,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,94; 31,39</t>
+          <t>20,91; 31,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,28; 28,42</t>
+          <t>19,41; 28,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,34; 36,01</t>
+          <t>28,1; 35,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,13; 18,12</t>
+          <t>12,99; 18,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,53; 21,35</t>
+          <t>15,67; 21,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,87; 24,61</t>
+          <t>18,22; 24,4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,51; 27,53</t>
+          <t>22,37; 27,73</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,08; 19,86</t>
+          <t>12,04; 20,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,25; 22,37</t>
+          <t>14,44; 22,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,79; 21,55</t>
+          <t>14,03; 21,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,89; 24,55</t>
+          <t>17,0; 24,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,28; 27,78</t>
+          <t>18,53; 27,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,12; 38,76</t>
+          <t>27,05; 37,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,33; 30,65</t>
+          <t>21,7; 30,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,87; 35,75</t>
+          <t>27,95; 36,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,38; 22,3</t>
+          <t>16,54; 22,11</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,41; 28,22</t>
+          <t>21,1; 27,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,62; 24,88</t>
+          <t>18,58; 24,86</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,08; 28,77</t>
+          <t>23,22; 28,54</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,15; 15,71</t>
+          <t>10,1; 15,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,82; 24,75</t>
+          <t>17,77; 24,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,7; 23,58</t>
+          <t>16,66; 23,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,36; 29,03</t>
+          <t>7,18; 29,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,53; 30,16</t>
+          <t>17,58; 31,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,96; 34,27</t>
+          <t>22,72; 34,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,51; 43,9</t>
+          <t>28,23; 44,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>41,17; 53,64</t>
+          <t>41,0; 53,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,96; 18,21</t>
+          <t>12,77; 18,22</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,48; 26,4</t>
+          <t>20,28; 26,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20,63; 27,26</t>
+          <t>20,75; 27,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,2; 34,44</t>
+          <t>11,03; 34,2</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,33; 18,51</t>
+          <t>14,41; 18,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,05; 23,15</t>
+          <t>18,07; 22,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,56; 22,27</t>
+          <t>17,42; 22,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,8; 31,62</t>
+          <t>25,79; 31,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,2; 25,02</t>
+          <t>18,58; 24,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,62; 33,63</t>
+          <t>26,87; 33,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,58; 32,02</t>
+          <t>25,89; 32,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,93; 74,32</t>
+          <t>37,73; 71,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,52; 19,99</t>
+          <t>16,57; 20,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,13; 26,29</t>
+          <t>22,45; 26,26</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,76; 25,59</t>
+          <t>21,76; 25,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,26; 56,17</t>
+          <t>32,3; 59,41</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,74; 17,71</t>
+          <t>10,61; 17,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,45; 21,43</t>
+          <t>14,64; 21,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,7; 22,06</t>
+          <t>15,69; 22,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,79; 31,29</t>
+          <t>23,21; 31,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,48; 30,79</t>
+          <t>23,18; 30,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,86; 41,84</t>
+          <t>34,74; 42,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,81; 39,99</t>
+          <t>32,58; 39,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>31,28; 49,48</t>
+          <t>33,18; 49,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,66; 24,92</t>
+          <t>19,57; 25,35</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27,57; 33,02</t>
+          <t>27,43; 32,68</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25,84; 31,08</t>
+          <t>25,52; 30,51</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,99; 41,32</t>
+          <t>30,47; 41,38</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,9; 9,35</t>
+          <t>3,91; 9,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,62; 10,75</t>
+          <t>4,62; 10,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,25; 17,47</t>
+          <t>9,27; 17,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,14; 23,47</t>
+          <t>7,38; 23,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,36; 27,35</t>
+          <t>22,57; 27,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33,35; 39,13</t>
+          <t>33,34; 39,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,56; 35,66</t>
+          <t>30,06; 35,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35,43; 41,8</t>
+          <t>35,51; 41,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,17; 23,45</t>
+          <t>19,3; 23,41</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28,32; 33,21</t>
+          <t>28,2; 33,38</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26,04; 31,36</t>
+          <t>26,38; 31,3</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>29,37; 35,6</t>
+          <t>29,24; 35,4</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,71; 15,19</t>
+          <t>12,71; 15,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,55; 19,27</t>
+          <t>16,55; 19,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,61; 20,22</t>
+          <t>17,44; 20,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,33; 24,93</t>
+          <t>17,7; 24,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,33; 25,25</t>
+          <t>22,46; 25,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,86; 35,21</t>
+          <t>31,78; 35,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,39; 32,71</t>
+          <t>29,4; 32,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37,95; 52,93</t>
+          <t>37,96; 53,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,01; 19,9</t>
+          <t>18,01; 19,96</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24,67; 26,84</t>
+          <t>24,74; 26,87</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23,98; 26,11</t>
+          <t>24,04; 26,14</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29,53; 38,32</t>
+          <t>29,2; 39,14</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>43830; 72862</t>
+          <t>46368; 73120</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>43449; 74901</t>
+          <t>42593; 72608</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69172; 102297</t>
+          <t>68462; 102693</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>77566; 114408</t>
+          <t>76905; 115335</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>49035; 76894</t>
+          <t>48677; 76951</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>65859; 98702</t>
+          <t>65759; 98580</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>66905; 98632</t>
+          <t>67348; 98345</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>126811; 161144</t>
+          <t>125733; 160615</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>102477; 141412</t>
+          <t>101389; 142275</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>116703; 160446</t>
+          <t>117797; 159131</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>146489; 190986</t>
+          <t>141390; 189395</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>214487; 262240</t>
+          <t>213122; 264221</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44316; 72880</t>
+          <t>44194; 73772</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59446; 93284</t>
+          <t>60203; 94021</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52020; 81279</t>
+          <t>52927; 82256</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>76378; 110996</t>
+          <t>76881; 111643</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>67987; 103315</t>
+          <t>68905; 101209</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>91415; 130630</t>
+          <t>91165; 126353</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79418; 114113</t>
+          <t>80776; 114848</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>106634; 136761</t>
+          <t>106927; 138636</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>120982; 164739</t>
+          <t>122227; 163335</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>161414; 212761</t>
+          <t>159076; 208702</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>139566; 186458</t>
+          <t>139244; 186305</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>192688; 240132</t>
+          <t>193854; 238291</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>55030; 85198</t>
+          <t>54760; 84739</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>111977; 155512</t>
+          <t>111675; 154987</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>87166; 123062</t>
+          <t>86964; 123248</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42529; 194014</t>
+          <t>47991; 195026</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>29405; 50595</t>
+          <t>29488; 52189</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>56643; 88402</t>
+          <t>58597; 88798</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47355; 72936</t>
+          <t>46897; 73681</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>68711; 89533</t>
+          <t>68438; 89012</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>92032; 129287</t>
+          <t>90691; 129407</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181473; 233978</t>
+          <t>179757; 233915</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>141956; 187586</t>
+          <t>142797; 188660</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>85162; 287618</t>
+          <t>92097; 285635</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>177392; 229260</t>
+          <t>178429; 229994</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>208872; 267875</t>
+          <t>209181; 265148</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>201864; 256003</t>
+          <t>200283; 257768</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>267019; 327211</t>
+          <t>266931; 330128</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>137122; 178702</t>
+          <t>132703; 176676</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>204082; 257841</t>
+          <t>205966; 255148</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>211267; 264464</t>
+          <t>213813; 264417</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>370988; 726877</t>
+          <t>369053; 695500</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>322634; 390280</t>
+          <t>323638; 394746</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>425864; 505747</t>
+          <t>431849; 505289</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>429785; 505479</t>
+          <t>429790; 509965</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>649331; 1130587</t>
+          <t>650127; 1195798</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>37540; 61901</t>
+          <t>37080; 62618</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>73761; 109398</t>
+          <t>74729; 110040</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>97421; 136942</t>
+          <t>97368; 137398</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>108263; 148633</t>
+          <t>110249; 150591</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>133541; 175105</t>
+          <t>131848; 174746</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>265071; 318172</t>
+          <t>264192; 320390</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>242250; 295250</t>
+          <t>240520; 291230</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>262418; 415123</t>
+          <t>278410; 418190</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>180495; 228838</t>
+          <t>179672; 232771</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>350460; 419760</t>
+          <t>348663; 415332</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>351143; 422304</t>
+          <t>346793; 414600</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>407281; 542961</t>
+          <t>400405; 543791</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11627; 27883</t>
+          <t>11656; 27200</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12270; 28577</t>
+          <t>12292; 27720</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26550; 50158</t>
+          <t>26618; 51518</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17169; 56444</t>
+          <t>17749; 55648</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>279175; 341506</t>
+          <t>281788; 343036</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>368901; 432898</t>
+          <t>368787; 435593</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>319826; 385891</t>
+          <t>325245; 388116</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>269334; 317763</t>
+          <t>269898; 316226</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>296512; 362706</t>
+          <t>298510; 362198</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>388534; 455611</t>
+          <t>386883; 457993</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>356537; 429399</t>
+          <t>361204; 428615</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>293942; 356244</t>
+          <t>292633; 354209</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>415562; 496675</t>
+          <t>415575; 493671</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>565369; 658184</t>
+          <t>565363; 658090</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>596353; 684670</t>
+          <t>590418; 681638</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>585173; 841542</t>
+          <t>597696; 842135</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>754211; 853079</t>
+          <t>758649; 858134</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1128697; 1247306</t>
+          <t>1125788; 1243950</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1038094; 1155304</t>
+          <t>1038332; 1157172</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1356466; 1891783</t>
+          <t>1356729; 1900198</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1197169; 1322679</t>
+          <t>1197307; 1326977</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1716913; 1867910</t>
+          <t>1721812; 1870194</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1659087; 1805842</t>
+          <t>1663220; 1808228</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2052127; 2663134</t>
+          <t>2029388; 2720438</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A02-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A02-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,79; 15,43</t>
+          <t>9,57; 15,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,74; 16,61</t>
+          <t>9,79; 16,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,96; 23,93</t>
+          <t>16,15; 23,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,22; 22,83</t>
+          <t>16,37; 23,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,87; 25,09</t>
+          <t>16,29; 25,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,91; 31,35</t>
+          <t>20,89; 31,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,41; 28,34</t>
+          <t>19,56; 28,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,1; 35,89</t>
+          <t>27,6; 34,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,99; 18,23</t>
+          <t>12,95; 18,4</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,67; 21,17</t>
+          <t>15,74; 21,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,22; 24,4</t>
+          <t>18,58; 24,67</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,37; 27,73</t>
+          <t>22,43; 27,37</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,04; 20,11</t>
+          <t>12,32; 20,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,44; 22,55</t>
+          <t>14,55; 22,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,03; 21,81</t>
+          <t>13,57; 21,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,0; 24,69</t>
+          <t>16,33; 23,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,53; 27,22</t>
+          <t>18,4; 27,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,05; 37,49</t>
+          <t>26,87; 38,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,7; 30,85</t>
+          <t>20,93; 30,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,95; 36,24</t>
+          <t>27,8; 35,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,54; 22,11</t>
+          <t>16,31; 22,28</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,1; 27,68</t>
+          <t>21,05; 27,57</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,58; 24,86</t>
+          <t>18,82; 24,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,22; 28,54</t>
+          <t>22,72; 28,1</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,1; 15,62</t>
+          <t>10,38; 15,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,77; 24,67</t>
+          <t>17,82; 25,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,66; 23,61</t>
+          <t>16,54; 23,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,18; 29,18</t>
+          <t>23,55; 32,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,58; 31,1</t>
+          <t>17,25; 30,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,72; 34,43</t>
+          <t>22,95; 34,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,23; 44,35</t>
+          <t>28,23; 43,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>41,0; 53,33</t>
+          <t>40,47; 53,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,77; 18,22</t>
+          <t>12,94; 18,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,28; 26,39</t>
+          <t>20,52; 26,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20,75; 27,42</t>
+          <t>20,67; 27,12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,03; 34,2</t>
+          <t>29,56; 36,58</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>32,9%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,41; 18,57</t>
+          <t>14,29; 18,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,07; 22,91</t>
+          <t>17,95; 22,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,42; 22,42</t>
+          <t>17,59; 22,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,79; 31,9</t>
+          <t>25,62; 31,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,58; 24,73</t>
+          <t>18,45; 24,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,87; 33,28</t>
+          <t>26,85; 33,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,89; 32,02</t>
+          <t>25,53; 32,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,73; 71,11</t>
+          <t>35,96; 41,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,57; 20,22</t>
+          <t>16,81; 20,1</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,45; 26,26</t>
+          <t>22,23; 26,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,76; 25,81</t>
+          <t>21,7; 25,61</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,3; 59,41</t>
+          <t>30,95; 35,11</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>38,77%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,61; 17,91</t>
+          <t>10,65; 18,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,64; 21,55</t>
+          <t>14,83; 21,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,69; 22,14</t>
+          <t>15,9; 21,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23,21; 31,7</t>
+          <t>21,57; 29,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,18; 30,72</t>
+          <t>23,38; 30,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,74; 42,13</t>
+          <t>34,65; 41,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,58; 39,45</t>
+          <t>32,5; 39,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>33,18; 49,84</t>
+          <t>45,11; 50,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,57; 25,35</t>
+          <t>19,29; 24,89</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27,43; 32,68</t>
+          <t>27,6; 32,98</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25,52; 30,51</t>
+          <t>25,77; 30,57</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,47; 41,38</t>
+          <t>36,27; 41,22</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,78%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,91; 9,12</t>
+          <t>3,62; 9,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,62; 10,43</t>
+          <t>4,53; 10,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,27; 17,94</t>
+          <t>9,07; 17,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,38; 23,14</t>
+          <t>5,98; 18,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,57; 27,47</t>
+          <t>22,5; 27,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33,34; 39,38</t>
+          <t>33,37; 39,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,06; 35,87</t>
+          <t>30,02; 35,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35,51; 41,6</t>
+          <t>34,31; 40,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,3; 23,41</t>
+          <t>19,3; 23,45</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28,2; 33,38</t>
+          <t>28,25; 33,48</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26,38; 31,3</t>
+          <t>26,05; 31,2</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>29,24; 35,4</t>
+          <t>28,89; 34,79</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>31,77%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,71; 15,1</t>
+          <t>12,78; 15,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,55; 19,26</t>
+          <t>16,64; 19,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,44; 20,13</t>
+          <t>17,46; 20,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,7; 24,94</t>
+          <t>22,4; 25,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,46; 25,4</t>
+          <t>22,5; 25,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,78; 35,11</t>
+          <t>31,92; 35,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,4; 32,77</t>
+          <t>29,18; 32,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37,96; 53,16</t>
+          <t>37,82; 40,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,01; 19,96</t>
+          <t>18,14; 20,03</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24,74; 26,87</t>
+          <t>24,82; 26,96</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24,04; 26,14</t>
+          <t>24,09; 26,14</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29,2; 39,14</t>
+          <t>30,73; 32,85</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94244</t>
+          <t>107558</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>143254</t>
+          <t>152673</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>237498</t>
+          <t>260231</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>46368; 73120</t>
+          <t>45337; 72810</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42593; 72608</t>
+          <t>42798; 71682</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68462; 102693</t>
+          <t>69278; 101540</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>76905; 115335</t>
+          <t>90155; 128427</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>48677; 76951</t>
+          <t>49947; 77605</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>65759; 98580</t>
+          <t>65694; 97791</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>67348; 98345</t>
+          <t>67886; 99112</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>125733; 160615</t>
+          <t>134800; 168444</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>101389; 142275</t>
+          <t>101106; 143576</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>117797; 159131</t>
+          <t>118304; 159548</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>141390; 189395</t>
+          <t>144182; 191485</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>213122; 264221</t>
+          <t>233068; 284379</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93446</t>
+          <t>95336</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>122005</t>
+          <t>133481</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>215451</t>
+          <t>228817</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44194; 73772</t>
+          <t>45208; 73681</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60203; 94021</t>
+          <t>60663; 94311</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52927; 82256</t>
+          <t>51205; 82195</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>76881; 111643</t>
+          <t>78921; 113792</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>68905; 101209</t>
+          <t>68434; 101313</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>91165; 126353</t>
+          <t>90577; 128189</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>80776; 114848</t>
+          <t>77920; 114360</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>106927; 138636</t>
+          <t>117615; 151172</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>122227; 163335</t>
+          <t>120500; 164620</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>159076; 208702</t>
+          <t>158701; 207919</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>139244; 186305</t>
+          <t>141086; 185503</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>193854; 238291</t>
+          <t>205903; 254722</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>117832</t>
+          <t>130750</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>78878</t>
+          <t>87361</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>196710</t>
+          <t>218111</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>54760; 84739</t>
+          <t>56312; 86001</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>111675; 154987</t>
+          <t>111980; 157171</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>86964; 123248</t>
+          <t>86325; 122198</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47991; 195026</t>
+          <t>111072; 151842</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>29488; 52189</t>
+          <t>28942; 51237</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58597; 88798</t>
+          <t>59205; 89770</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>46897; 73681</t>
+          <t>46894; 72758</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>68438; 89012</t>
+          <t>75884; 100159</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>90691; 129407</t>
+          <t>91922; 130389</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>179757; 233915</t>
+          <t>181893; 235632</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>142797; 188660</t>
+          <t>142226; 186623</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>92097; 285635</t>
+          <t>194808; 241120</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>297376</t>
+          <t>320654</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>505168</t>
+          <t>335075</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>802544</t>
+          <t>655728</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>178429; 229994</t>
+          <t>176971; 227684</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>209181; 265148</t>
+          <t>207695; 262213</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>200283; 257768</t>
+          <t>202224; 257476</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>266931; 330128</t>
+          <t>289938; 352879</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>132703; 176676</t>
+          <t>131820; 177438</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>205966; 255148</t>
+          <t>205827; 257576</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>213813; 264417</t>
+          <t>210817; 266713</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>369053; 695500</t>
+          <t>309657; 358529</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>323638; 394746</t>
+          <t>328190; 392470</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>431849; 505289</t>
+          <t>427775; 505519</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>429790; 509965</t>
+          <t>428635; 505969</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>650127; 1195798</t>
+          <t>616887; 699698</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>129047</t>
+          <t>143733</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>365777</t>
+          <t>398331</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>494823</t>
+          <t>542064</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>37080; 62618</t>
+          <t>37229; 62935</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>74729; 110040</t>
+          <t>75696; 108084</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>97368; 137398</t>
+          <t>98706; 134734</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>110249; 150591</t>
+          <t>122505; 167212</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>131848; 174746</t>
+          <t>132989; 174774</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>264192; 320390</t>
+          <t>263484; 317460</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>240520; 291230</t>
+          <t>239916; 291887</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>278410; 418190</t>
+          <t>374454; 421292</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>179672; 232771</t>
+          <t>177163; 228527</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>348663; 415332</t>
+          <t>350772; 419184</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>346793; 414600</t>
+          <t>350197; 415392</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>400405; 543791</t>
+          <t>507156; 576286</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31244</t>
+          <t>26333</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>292731</t>
+          <t>317005</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>323975</t>
+          <t>343338</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11656; 27200</t>
+          <t>10800; 27558</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12292; 27720</t>
+          <t>12050; 28072</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26618; 51518</t>
+          <t>26045; 50677</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17749; 55648</t>
+          <t>14183; 44130</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>281788; 343036</t>
+          <t>280983; 344320</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>368787; 435593</t>
+          <t>369132; 431611</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>325245; 388116</t>
+          <t>324833; 384888</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>269898; 316226</t>
+          <t>289265; 342450</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>298510; 362198</t>
+          <t>298604; 362786</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>386883; 457993</t>
+          <t>387621; 459346</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>361204; 428615</t>
+          <t>356725; 427184</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>292633; 354209</t>
+          <t>312082; 375803</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>763190</t>
+          <t>824363</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1507812</t>
+          <t>1423927</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2271002</t>
+          <t>2248290</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>415575; 493671</t>
+          <t>417754; 498621</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>565363; 658090</t>
+          <t>568332; 655853</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>590418; 681638</t>
+          <t>591144; 686530</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>597696; 842135</t>
+          <t>771100; 878557</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>758649; 858134</t>
+          <t>760035; 856955</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1125788; 1243950</t>
+          <t>1130887; 1247010</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1038332; 1157172</t>
+          <t>1030494; 1149512</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1356729; 1900198</t>
+          <t>1374304; 1476599</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1197307; 1326977</t>
+          <t>1205893; 1331391</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1721812; 1870194</t>
+          <t>1727177; 1876322</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1663220; 1808228</t>
+          <t>1666324; 1808375</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2029388; 2720438</t>
+          <t>2174686; 2324235</t>
         </is>
       </c>
     </row>
